--- a/03_Outputs/all/01_TablasDescriptivas/idx12_salud_vr.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx12_salud_vr.xlsx
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>1.091492842546406</v>
+        <v>1.091492842546405</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.4475374866234385</v>
+        <v>0.4475374866234383</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>39.85083393198149</v>
+        <v>39.85083393198152</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>27.28732106366015</v>
+        <v>27.28732106366013</v>
       </c>
       <c r="C11">
         <v>2</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>21.67340783877239</v>
+        <v>21.6734078387724</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>39.85083393198149</v>
+        <v>39.85083393198152</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>67.13815499564164</v>
+        <v>67.13815499564166</v>
       </c>
       <c r="C15">
         <v>2</v>
